--- a/carga/planificacion 2526.xlsx
+++ b/carga/planificacion 2526.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Nueva carpeta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFBBFA75-483A-42A2-9F62-A7563731C1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4071E6B4-AB79-4024-951B-0C67AA7F6450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{55593E05-E3D7-4927-BAB9-75E6C943F882}"/>
   </bookViews>
@@ -79,9 +79,6 @@
     <t>Lote 8A (Norte)</t>
   </si>
   <si>
-    <t xml:space="preserve">Vicia+Triticale </t>
-  </si>
-  <si>
     <t>Soja 2°</t>
   </si>
   <si>
@@ -155,6 +152,9 @@
   </si>
   <si>
     <t>Lote 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vicia-Triticale </t>
   </si>
 </sst>
 </file>
@@ -600,6 +600,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F24F6059-C4E9-4ACF-92AE-F682146464C8}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -742,7 +745,7 @@
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="8" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>16</v>
@@ -760,10 +763,10 @@
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>18</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>19</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>10</v>
@@ -778,10 +781,10 @@
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>10</v>
@@ -796,10 +799,10 @@
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>10</v>
@@ -814,10 +817,10 @@
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>10</v>
@@ -832,7 +835,7 @@
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -855,7 +858,7 @@
         <v>8</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>10</v>
@@ -870,10 +873,10 @@
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>10</v>
@@ -888,10 +891,10 @@
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>10</v>
@@ -909,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>10</v>
@@ -927,7 +930,7 @@
         <v>12</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>10</v>
@@ -945,7 +948,7 @@
         <v>12</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>10</v>
@@ -963,7 +966,7 @@
         <v>8</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>10</v>
@@ -981,7 +984,7 @@
         <v>8</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>10</v>
@@ -996,7 +999,7 @@
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="4"/>
@@ -1009,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>10</v>
@@ -1027,7 +1030,7 @@
         <v>12</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>10</v>
@@ -1045,7 +1048,7 @@
         <v>12</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>10</v>
@@ -1063,7 +1066,7 @@
         <v>15</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>10</v>
@@ -1081,7 +1084,7 @@
         <v>15</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>10</v>
@@ -1099,7 +1102,7 @@
         <v>15</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>10</v>
@@ -1114,13 +1117,13 @@
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="13"/>
       <c r="B33" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="D33" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>39</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>11</v>
@@ -1132,10 +1135,10 @@
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="13"/>
       <c r="B34" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>10</v>
@@ -1150,10 +1153,10 @@
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="13"/>
       <c r="B35" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="9" t="s">
         <v>40</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>41</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>10</v>
@@ -1168,7 +1171,7 @@
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="13"/>
       <c r="B36" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>13</v>
@@ -1186,7 +1189,7 @@
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="13"/>
       <c r="B37" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>14</v>
@@ -1204,10 +1207,10 @@
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="13"/>
       <c r="B38" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>10</v>
@@ -1225,7 +1228,7 @@
         <v>12</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>10</v>
